--- a/data/civ_rp_2021/data/coderef.xlsx
+++ b/data/civ_rp_2021/data/coderef.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/claudegrasland1/worldregio/afromapr/data/civ_rp_2021/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83FE512B-0B38-9C42-9A97-E7874E80A26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF0680D7-C474-8046-A10F-D4638ED088AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3260" yWindow="2160" windowWidth="28040" windowHeight="17440" xr2:uid="{9CBA2E57-0AB7-7747-9074-2CFFD207C343}"/>
+    <workbookView xWindow="3260" yWindow="2160" windowWidth="28040" windowHeight="17440" xr2:uid="{149F3155-6D0F-AA43-8E20-BDB3A0284B23}"/>
   </bookViews>
   <sheets>
     <sheet name="coderef" sheetId="1" r:id="rId1"/>
@@ -5914,7 +5914,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6543C922-B743-DA44-BD88-05867C9C4627}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75D7A24E-73EB-7342-B03F-431C2FB148F1}">
   <dimension ref="A1:I511"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -18733,7 +18733,7 @@
         <v>61527</v>
       </c>
       <c r="I442">
-        <v>111766</v>
+        <v>11176</v>
       </c>
     </row>
     <row r="443" spans="1:9" x14ac:dyDescent="0.2">
